--- a/data/raw/Copa_2026_2027/boxscores/FCBQ_PBP_U.E._CLARET_A_vs_CE_PALAMOS_CAN_PACO_81-75_analysis.xlsx
+++ b/data/raw/Copa_2026_2027/boxscores/FCBQ_PBP_U.E._CLARET_A_vs_CE_PALAMOS_CAN_PACO_81-75_analysis.xlsx
@@ -567,73 +567,73 @@
         <v>90.02</v>
       </c>
       <c r="C2" s="2" t="n">
+        <v>87.76000000000001</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>83.31</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>87.76000000000001</v>
-      </c>
       <c r="E2" s="2" t="n">
-        <v>51.52</v>
+        <v>45.65</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>25.5</v>
+        <v>25.23</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>22.5</v>
+        <v>35.56</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P2" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="R2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>43.33</v>
+        <v>41.38</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>22.22</v>
+        <v>45.45</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>44.44</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="3">
@@ -646,73 +646,73 @@
         <v>90.02</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>83.31</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>87.76000000000001</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>83.31</v>
-      </c>
       <c r="E3" s="2" t="n">
-        <v>45.65</v>
+        <v>51.52</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>25.23</v>
+        <v>25.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>35.56</v>
+        <v>22.5</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="I3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>41.38</v>
+        <v>43.33</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>45.45</v>
+        <v>22.22</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>26.09</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="4"/>
@@ -954,29 +954,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#0 GUILLEM BAO OLIVERAS</t>
+          <t>#2 JORDI POCH CAMPABADAL</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>4</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>0</v>
@@ -1006,13 +1006,13 @@
         <v>1</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
@@ -1021,13 +1021,13 @@
         <v>0</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>0</v>
@@ -1042,82 +1042,82 @@
         <v>0</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AM8" s="2" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>66.67</v>
+        <v>58.14</v>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ8" s="2" t="n">
-        <v>25</v>
+        <v>22.52</v>
       </c>
       <c r="AR8" s="2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AS8" s="2" t="n">
-        <v>19.86</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>#1 NIELS GEERS ESCALONA</t>
+          <t>#3 SOWKIN SHETTY</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>0</v>
@@ -1141,34 +1141,34 @@
         <v>0</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF9" s="3" t="n">
         <v>0</v>
@@ -1198,45 +1198,45 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>22:26</t>
+        </is>
+      </c>
+      <c r="AM9" s="2" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="AN9" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>00:48</t>
-        </is>
-      </c>
-      <c r="AM9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN9" s="2" t="n">
-        <v>150</v>
-      </c>
       <c r="AO9" s="2" t="n">
-        <v>150</v>
+        <v>86.63</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>3</v>
+        <v>1.54</v>
       </c>
       <c r="AQ9" s="2" t="n">
-        <v>0</v>
+        <v>11.01</v>
       </c>
       <c r="AR9" s="2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS9" s="2" t="n">
-        <v>51.4</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>#2 GENÍS CABELLO ALBERT</t>
+          <t>#4 SERGI CARRASCO LEON</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1246,13 +1246,13 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -1282,10 +1282,10 @@
         <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>0</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="2" t="n">
         <v>0</v>
@@ -1342,18 +1342,18 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>01:39</t>
         </is>
       </c>
       <c r="AM10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN10" s="2" t="n">
         <v>0</v>
@@ -1365,19 +1365,19 @@
         <v>0</v>
       </c>
       <c r="AQ10" s="2" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="AR10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AS10" s="2" t="n">
-        <v>14.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>#3 DAN GINER FALGUERAS</t>
+          <t>#5 HECTOR GIMENEZ ANTON</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1387,13 +1387,13 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -1423,79 +1423,79 @@
         <v>0</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="AM11" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AM11" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="AN11" s="2" t="n">
         <v>0</v>
       </c>
@@ -1506,41 +1506,41 @@
         <v>0</v>
       </c>
       <c r="AQ11" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AR11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AS11" s="2" t="n">
-        <v>13.17</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>#4 BERNAT BAO OLIVERAS</t>
+          <t>#6 MARTI GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1570,28 +1570,28 @@
         <v>1</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0</v>
@@ -1603,79 +1603,79 @@
         <v>0</v>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>06:44</t>
+        </is>
+      </c>
+      <c r="AM12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="AF12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH12" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AI12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>20:22</t>
-        </is>
-      </c>
-      <c r="AM12" s="2" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AN12" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AO12" s="2" t="n">
-        <v>45.96</v>
-      </c>
-      <c r="AP12" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AQ12" s="2" t="n">
-        <v>8.42</v>
-      </c>
       <c r="AR12" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AS12" s="2" t="n">
-        <v>23.99</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>#6 FRANC JUANOLA AGUILA</t>
+          <t>#7 ADRIA TORROJA CORBELLA</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -1705,25 +1705,25 @@
         <v>0</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>1</v>
@@ -1744,13 +1744,13 @@
         <v>0</v>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AE13" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF13" s="3" t="n">
         <v>0</v>
@@ -1762,118 +1762,118 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK13" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>31:09</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AM13" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN13" s="2" t="n">
-        <v>16.67</v>
+        <v>43.75</v>
       </c>
       <c r="AO13" s="2" t="n">
-        <v>16.67</v>
+        <v>43.75</v>
       </c>
       <c r="AP13" s="2" t="n">
-        <v>0.33</v>
+        <v>0.78</v>
       </c>
       <c r="AQ13" s="2" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="AR13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AS13" s="2" t="n">
-        <v>7.92</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>#7 JOSE LÓPEZ MARTÍNEZ</t>
+          <t>#9 ARMAK KARIMI GONZALEZ</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="Y14" s="2" t="n">
-        <v>57.14</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>0</v>
@@ -1885,13 +1885,13 @@
         <v>0</v>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="2" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="n">
         <v>0</v>
@@ -1906,205 +1906,205 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>23:34</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AM14" s="2" t="n">
-        <v>12.64</v>
+        <v>6.76</v>
       </c>
       <c r="AN14" s="2" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="2" t="n">
-        <v>59.34</v>
+        <v>14.79</v>
       </c>
       <c r="AP14" s="2" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="AQ14" s="2" t="n">
-        <v>7.33</v>
+        <v>0</v>
       </c>
       <c r="AR14" s="2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AS14" s="2" t="n">
-        <v>23.8</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>#9 EDUARD ILLA MARTINEZ</t>
+          <t>#12 ORIOL ABY TASCÓN MARQUIÉ</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="n">
+      <c r="AH15" s="2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AI15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ15" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AK15" s="2" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AM15" s="2" t="n">
-        <v>5</v>
+        <v>11.88</v>
       </c>
       <c r="AN15" s="2" t="n">
-        <v>30</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AO15" s="2" t="n">
-        <v>30</v>
+        <v>71.55</v>
       </c>
       <c r="AP15" s="2" t="n">
-        <v>0.6</v>
+        <v>1.43</v>
       </c>
       <c r="AQ15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR15" s="2" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AS15" s="2" t="n">
-        <v>19.64</v>
+        <v>29.32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>#10 XAVI MAIXENCHS BOBE</t>
+          <t>#15 ALBERT SITJES LOZANO</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0</v>
@@ -2134,28 +2134,28 @@
         <v>1</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="U16" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="Y16" s="2" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>0</v>
@@ -2170,82 +2170,82 @@
         <v>0</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ16" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AK16" s="2" t="n">
-        <v>66.67</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>27:05</t>
+          <t>29:34</t>
         </is>
       </c>
       <c r="AM16" s="2" t="n">
-        <v>11.32</v>
+        <v>10.64</v>
       </c>
       <c r="AN16" s="2" t="n">
-        <v>75</v>
+        <v>12.5</v>
       </c>
       <c r="AO16" s="2" t="n">
-        <v>66.25</v>
+        <v>28.2</v>
       </c>
       <c r="AP16" s="2" t="n">
-        <v>1.22</v>
+        <v>0.52</v>
       </c>
       <c r="AQ16" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="AR16" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AS16" s="2" t="n">
-        <v>18.71</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>#15 JOAN ODENA MASSAGUER</t>
+          <t>#44 GONZALO FERNANDO BADAL</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0</v>
@@ -2269,19 +2269,19 @@
         <v>0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>0</v>
@@ -2290,103 +2290,103 @@
         <v>2</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Y17" s="2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="Z17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE17" s="2" t="n">
+      <c r="AF17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>30:50</t>
+        </is>
+      </c>
+      <c r="AM17" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="AN17" s="2" t="n">
         <v>66.67</v>
       </c>
-      <c r="AF17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ17" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK17" s="2" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>30:16</t>
-        </is>
-      </c>
-      <c r="AM17" s="2" t="n">
-        <v>15.76</v>
-      </c>
-      <c r="AN17" s="2" t="n">
-        <v>53.57</v>
-      </c>
       <c r="AO17" s="2" t="n">
-        <v>53.93</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="AP17" s="2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AQ17" s="2" t="n">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="AR17" s="2" t="n">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="AS17" s="2" t="n">
-        <v>22.77</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>#17 BRU POSTIGO CAMPRUBI</t>
+          <t>#77 ADRIÀ ORDOBÀS BENGADO</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
         <v>6</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>0</v>
@@ -2422,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>0</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>0</v>
@@ -2458,70 +2458,70 @@
         <v>0</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH18" s="2" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AJ18" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK18" s="2" t="n">
-        <v>50</v>
+        <v>16.67</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AM18" s="2" t="n">
-        <v>4.44</v>
+        <v>9</v>
       </c>
       <c r="AN18" s="2" t="n">
-        <v>62.5</v>
+        <v>33.33</v>
       </c>
       <c r="AO18" s="2" t="n">
-        <v>67.56999999999999</v>
+        <v>33.33</v>
       </c>
       <c r="AP18" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AQ18" s="2" t="n">
-        <v>40.32</v>
+        <v>25</v>
       </c>
       <c r="AR18" s="2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AS18" s="2" t="n">
-        <v>15.7</v>
+        <v>32.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>#28 IAGO CARBAJO AUBESO</t>
+          <t>#87 JAVIER VICENTE NIETO</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
@@ -2557,28 +2557,28 @@
         <v>1</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>0</v>
@@ -2599,48 +2599,48 @@
         <v>0</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH19" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK19" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AM19" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AN19" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO19" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP19" s="2" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AQ19" s="2" t="n">
-        <v>50</v>
+        <v>11.11</v>
       </c>
       <c r="AR19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AS19" s="2" t="n">
-        <v>6.87</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="20">
@@ -2674,16 +2674,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>0</v>
@@ -2692,10 +2692,10 @@
         <v>0</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R20" s="3" t="n">
         <v>0</v>
@@ -2787,112 +2787,112 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C21" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K21" s="3" t="n">
+      <c r="U21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="X21" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>30</v>
-      </c>
       <c r="Y21" s="2" t="n">
-        <v>43.33</v>
+        <v>41.38</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF21" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AD21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE21" s="2" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="AF21" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="AG21" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH21" s="2" t="n">
-        <v>22.22</v>
+        <v>45.45</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AJ21" s="3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AK21" s="2" t="n">
-        <v>44.44</v>
+        <v>26.09</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
@@ -2900,22 +2900,22 @@
         </is>
       </c>
       <c r="AM21" s="2" t="n">
-        <v>73.04000000000001</v>
+        <v>80</v>
       </c>
       <c r="AN21" s="2" t="n">
-        <v>51.52</v>
+        <v>45.65</v>
       </c>
       <c r="AO21" s="2" t="n">
-        <v>51.34</v>
+        <v>49.38</v>
       </c>
       <c r="AP21" s="2" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="AQ21" s="2" t="n">
-        <v>25.5</v>
+        <v>25.23</v>
       </c>
       <c r="AR21" s="2" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="AS21" t="inlineStr"/>
     </row>
@@ -3159,29 +3159,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>#2 JORDI POCH CAMPABADAL</t>
+          <t>#0 GUILLEM BAO OLIVERAS</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
         <v>4</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0</v>
@@ -3211,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>0</v>
@@ -3226,13 +3226,13 @@
         <v>0</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>0</v>
@@ -3247,85 +3247,85 @@
         <v>0</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AF27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH27" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AM27" s="2" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AN27" s="2" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="AO27" s="2" t="n">
-        <v>58.14</v>
+        <v>66.67</v>
       </c>
       <c r="AP27" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AQ27" s="2" t="n">
-        <v>22.52</v>
+        <v>25</v>
       </c>
       <c r="AR27" s="2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AS27" s="2" t="n">
-        <v>9.539999999999999</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>#3 SOWKIN SHETTY</t>
+          <t>#1 NIELS GEERS ESCALONA</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>0</v>
@@ -3346,102 +3346,102 @@
         <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="Z28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE28" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>00:48</t>
         </is>
       </c>
       <c r="AM28" s="2" t="n">
-        <v>8.08</v>
+        <v>1</v>
       </c>
       <c r="AN28" s="2" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AO28" s="2" t="n">
-        <v>86.63</v>
+        <v>150</v>
       </c>
       <c r="AP28" s="2" t="n">
-        <v>1.54</v>
+        <v>3</v>
       </c>
       <c r="AQ28" s="2" t="n">
-        <v>11.01</v>
+        <v>0</v>
       </c>
       <c r="AR28" s="2" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AS28" s="2" t="n">
-        <v>15.25</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>#4 SERGI CARRASCO LEON</t>
+          <t>#2 GENÍS CABELLO ALBERT</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
@@ -3451,13 +3451,13 @@
         <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
@@ -3487,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>0</v>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" s="2" t="n">
         <v>0</v>
@@ -3547,18 +3547,18 @@
         <v>0</v>
       </c>
       <c r="AJ29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>01:39</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AM29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN29" s="2" t="n">
         <v>0</v>
@@ -3570,19 +3570,19 @@
         <v>0</v>
       </c>
       <c r="AQ29" s="2" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="AR29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AS29" s="2" t="n">
-        <v>0</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>#5 HECTOR GIMENEZ ANTON</t>
+          <t>#3 DAN GINER FALGUERAS</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
@@ -3592,13 +3592,13 @@
         <v>0</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0</v>
@@ -3628,10 +3628,10 @@
         <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>2</v>
@@ -3640,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>0</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="2" t="n">
         <v>0</v>
@@ -3688,18 +3688,18 @@
         <v>0</v>
       </c>
       <c r="AJ30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AM30" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN30" s="2" t="n">
         <v>0</v>
@@ -3711,41 +3711,41 @@
         <v>0</v>
       </c>
       <c r="AQ30" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AR30" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AS30" s="2" t="n">
-        <v>17.75</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>#6 MARTI GOMEZ GARCIA</t>
+          <t>#4 BERNAT BAO OLIVERAS</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0</v>
@@ -3775,28 +3775,28 @@
         <v>1</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>0</v>
@@ -3808,127 +3808,127 @@
         <v>0</v>
       </c>
       <c r="AC31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE31" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG31" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH31" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>06:44</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AM31" s="2" t="n">
-        <v>0</v>
+        <v>10.88</v>
       </c>
       <c r="AN31" s="2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AO31" s="2" t="n">
-        <v>0</v>
+        <v>45.96</v>
       </c>
       <c r="AP31" s="2" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AQ31" s="2" t="n">
-        <v>100</v>
+        <v>8.42</v>
       </c>
       <c r="AR31" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AS31" s="2" t="n">
-        <v>5.6</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>#7 ADRIA TORROJA CORBELLA</t>
+          <t>#6 FRANC JUANOLA AGUILA</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>5</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>1</v>
@@ -3949,13 +3949,13 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AE32" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="3" t="n">
         <v>0</v>
@@ -3967,136 +3967,136 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>31:09</t>
         </is>
       </c>
       <c r="AM32" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AN32" s="2" t="n">
-        <v>43.75</v>
+        <v>16.67</v>
       </c>
       <c r="AO32" s="2" t="n">
-        <v>43.75</v>
+        <v>16.67</v>
       </c>
       <c r="AP32" s="2" t="n">
-        <v>0.78</v>
+        <v>0.33</v>
       </c>
       <c r="AQ32" s="2" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="AR32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AS32" s="2" t="n">
-        <v>20.33</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>#9 ARMAK KARIMI GONZALEZ</t>
+          <t>#7 JOSE LÓPEZ MARTÍNEZ</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D33" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X33" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y33" s="2" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD33" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Y33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AE33" s="2" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="AF33" s="3" t="n">
         <v>0</v>
@@ -4111,487 +4111,487 @@
         <v>0</v>
       </c>
       <c r="AJ33" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>23:34</t>
         </is>
       </c>
       <c r="AM33" s="2" t="n">
-        <v>6.76</v>
+        <v>12.64</v>
       </c>
       <c r="AN33" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AO33" s="2" t="n">
-        <v>14.79</v>
+        <v>59.34</v>
       </c>
       <c r="AP33" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AQ33" s="2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AR33" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="AQ33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" s="2" t="n">
-        <v>0.4</v>
-      </c>
       <c r="AS33" s="2" t="n">
-        <v>12.34</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>#12 ORIOL ABY TASCÓN MARQUIÉ</t>
+          <t>#9 EDUARD ILLA MARTINEZ</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AM34" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG34" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH34" s="2" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="AI34" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ34" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK34" s="2" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AM34" s="2" t="n">
-        <v>11.88</v>
-      </c>
       <c r="AN34" s="2" t="n">
-        <v>68.18000000000001</v>
+        <v>30</v>
       </c>
       <c r="AO34" s="2" t="n">
-        <v>71.55</v>
+        <v>30</v>
       </c>
       <c r="AP34" s="2" t="n">
-        <v>1.43</v>
+        <v>0.6</v>
       </c>
       <c r="AQ34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AR34" s="2" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="AS34" s="2" t="n">
-        <v>29.32</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>#15 ALBERT SITJES LOZANO</t>
+          <t>#10 XAVI MAIXENCHS BOBE</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="3" t="n">
+      <c r="U35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH35" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="AJ35" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X35" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y35" s="2" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="AK35" s="2" t="n">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>29:34</t>
+          <t>27:05</t>
         </is>
       </c>
       <c r="AM35" s="2" t="n">
-        <v>10.64</v>
+        <v>11.32</v>
       </c>
       <c r="AN35" s="2" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="AO35" s="2" t="n">
-        <v>28.2</v>
+        <v>66.25</v>
       </c>
       <c r="AP35" s="2" t="n">
-        <v>0.52</v>
+        <v>1.22</v>
       </c>
       <c r="AQ35" s="2" t="n">
-        <v>8.59</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AR35" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AS35" s="2" t="n">
-        <v>14.83</v>
+        <v>18.71</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>#44 GONZALO FERNANDO BADAL</t>
+          <t>#15 JOAN ODENA MASSAGUER</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W36" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="X36" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC36" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD36" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE36" s="2" t="n">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="AF36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AG36" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AI36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ36" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK36" s="2" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>30:50</t>
+          <t>30:16</t>
         </is>
       </c>
       <c r="AM36" s="2" t="n">
-        <v>11.2</v>
+        <v>15.76</v>
       </c>
       <c r="AN36" s="2" t="n">
-        <v>66.67</v>
+        <v>53.57</v>
       </c>
       <c r="AO36" s="2" t="n">
-        <v>66.95999999999999</v>
+        <v>53.93</v>
       </c>
       <c r="AP36" s="2" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" s="2" t="n">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="AR36" s="2" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AS36" s="2" t="n">
-        <v>13.69</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>#77 ADRIÀ ORDOBÀS BENGADO</t>
+          <t>#17 BRU POSTIGO CAMPRUBI</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
         <v>6</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>0</v>
@@ -4636,13 +4636,13 @@
         <v>0</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y37" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>0</v>
@@ -4663,70 +4663,70 @@
         <v>0</v>
       </c>
       <c r="AF37" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH37" s="2" t="n">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AJ37" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AK37" s="2" t="n">
-        <v>16.67</v>
+        <v>50</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AM37" s="2" t="n">
-        <v>9</v>
+        <v>4.44</v>
       </c>
       <c r="AN37" s="2" t="n">
-        <v>33.33</v>
+        <v>62.5</v>
       </c>
       <c r="AO37" s="2" t="n">
-        <v>33.33</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="AP37" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AQ37" s="2" t="n">
-        <v>25</v>
+        <v>40.32</v>
       </c>
       <c r="AR37" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AS37" s="2" t="n">
-        <v>32.41</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>#87 JAVIER VICENTE NIETO</t>
+          <t>#28 IAGO CARBAJO AUBESO</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0</v>
@@ -4762,28 +4762,28 @@
         <v>1</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y38" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>0</v>
@@ -4804,48 +4804,48 @@
         <v>0</v>
       </c>
       <c r="AF38" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG38" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AM38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="AI38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ38" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK38" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>19:56</t>
-        </is>
-      </c>
-      <c r="AM38" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AN38" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO38" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP38" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AQ38" s="2" t="n">
-        <v>11.11</v>
-      </c>
       <c r="AR38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AS38" s="2" t="n">
-        <v>17.01</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="39">
@@ -4879,16 +4879,16 @@
         <v>0</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>0</v>
@@ -4897,10 +4897,10 @@
         <v>0</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -4992,112 +4992,112 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G40" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="I40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>27</v>
-      </c>
       <c r="R40" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="S40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="U40" s="3" t="n">
+      <c r="V40" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y40" s="2" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="Z40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC40" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="Y40" s="2" t="n">
-        <v>41.38</v>
-      </c>
-      <c r="Z40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="AD40" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE40" s="2" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="AF40" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG40" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>45.45</v>
+        <v>22.22</v>
       </c>
       <c r="AI40" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ40" s="3" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AK40" s="2" t="n">
-        <v>26.09</v>
+        <v>44.44</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
@@ -5105,22 +5105,22 @@
         </is>
       </c>
       <c r="AM40" s="2" t="n">
-        <v>80</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="AN40" s="2" t="n">
-        <v>45.65</v>
+        <v>51.52</v>
       </c>
       <c r="AO40" s="2" t="n">
-        <v>49.38</v>
+        <v>51.34</v>
       </c>
       <c r="AP40" s="2" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="AQ40" s="2" t="n">
-        <v>25.23</v>
+        <v>25.5</v>
       </c>
       <c r="AR40" s="2" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="AS40" t="inlineStr"/>
     </row>

--- a/data/raw/Copa_2026_2027/boxscores/FCBQ_PBP_U.E._CLARET_A_vs_CE_PALAMOS_CAN_PACO_81-75_analysis.xlsx
+++ b/data/raw/Copa_2026_2027/boxscores/FCBQ_PBP_U.E._CLARET_A_vs_CE_PALAMOS_CAN_PACO_81-75_analysis.xlsx
@@ -294,7 +294,7 @@
     <t>31:09</t>
   </si>
   <si>
-    <t>#7 JOSE FRANCISCO LÓPEZ MARTÍNEZ</t>
+    <t>#7 JOSÉ FRANCISCO LÓPEZ MARTÍNEZ</t>
   </si>
   <si>
     <t>23:34</t>
